--- a/Docs/sprint_plan_collective.xlsx
+++ b/Docs/sprint_plan_collective.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AB5A4DDF1250361EE946987449CC0E386371F7DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{763B62BE-F142-4C68-874F-6B44D6B11E30}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_AB5A4DDF1250361EE946987449CC0E386371F7DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64FDA453-3705-4BFD-9ED6-3B4333668185}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,6 +603,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
